--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2593,51 +2593,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135494439</v>
+        <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93367</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>852377</v>
+        <v>852499</v>
       </c>
       <c r="R19" t="n">
-        <v>7375395</v>
+        <v>7375394</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,27 +2658,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Under kolad stubbe med markkontakt</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,34 +2682,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494439</t>
+          <t>https://artportalen.se/Sighting/136948350</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135522430</v>
+        <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93375</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,21 +2716,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2749,13 +2740,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>852692</v>
+        <v>852538</v>
       </c>
       <c r="R20" t="n">
-        <v>7375409</v>
+        <v>7375399</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2779,22 +2770,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,60 +2805,63 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522430</t>
+          <t>https://artportalen.se/Sighting/136948353</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135494410</v>
+        <v>135494439</v>
       </c>
       <c r="B21" t="n">
-        <v>93007</v>
+        <v>93367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>852758</v>
+        <v>852377</v>
       </c>
       <c r="R21" t="n">
-        <v>7375446</v>
+        <v>7375395</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2896,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,7 +2900,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Under kolad stubbe med markkontakt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,6 +2914,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2932,38 +2932,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494410</t>
+          <t>https://artportalen.se/Sighting/135494439</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135494430</v>
+        <v>135522430</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>93375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>852122</v>
+        <v>852692</v>
       </c>
       <c r="R22" t="n">
-        <v>7375442</v>
+        <v>7375409</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,49 +3033,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494430</t>
+          <t>https://artportalen.se/Sighting/135522430</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135522445</v>
+        <v>135494410</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>93007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>852123</v>
+        <v>852758</v>
       </c>
       <c r="R23" t="n">
-        <v>7375442</v>
+        <v>7375446</v>
       </c>
       <c r="S23" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,49 +3145,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522445</t>
+          <t>https://artportalen.se/Sighting/135494410</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135494402</v>
+        <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>79468</v>
+        <v>93437</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>852696</v>
+        <v>852904</v>
       </c>
       <c r="R24" t="n">
-        <v>7375404</v>
+        <v>7375430</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,49 +3257,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494402</t>
+          <t>https://artportalen.se/Sighting/136948360</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135494411</v>
+        <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>79468</v>
+        <v>93449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>852712</v>
+        <v>852852</v>
       </c>
       <c r="R25" t="n">
-        <v>7375445</v>
+        <v>7375436</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3339,22 +3339,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,27 +3369,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494411</t>
+          <t>https://artportalen.se/Sighting/136948358</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135494431</v>
+        <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>80063</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>852101</v>
+        <v>852904</v>
       </c>
       <c r="R26" t="n">
-        <v>7375449</v>
+        <v>7375430</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3451,22 +3451,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,49 +3481,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494431</t>
+          <t>https://artportalen.se/Sighting/136948359</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135522443</v>
+        <v>135494430</v>
       </c>
       <c r="B27" t="n">
-        <v>80063</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>852263</v>
+        <v>852122</v>
       </c>
       <c r="R27" t="n">
-        <v>7375416</v>
+        <v>7375442</v>
       </c>
       <c r="S27" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,70 +3593,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522443</t>
+          <t>https://artportalen.se/Sighting/135494430</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135494438</v>
+        <v>135522445</v>
       </c>
       <c r="B28" t="n">
-        <v>57169</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>852178</v>
+        <v>852123</v>
       </c>
       <c r="R28" t="n">
-        <v>7375380</v>
+        <v>7375442</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3685,7 +3680,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3695,7 +3690,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,27 +3705,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494438</t>
+          <t>https://artportalen.se/Sighting/135522445</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136044719</v>
+        <v>135494402</v>
       </c>
       <c r="B29" t="n">
-        <v>57193</v>
+        <v>79468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,42 +3733,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>852790</v>
+        <v>852696</v>
       </c>
       <c r="R29" t="n">
-        <v>7375455</v>
+        <v>7375404</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3797,12 +3787,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3817,49 +3817,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136044719</t>
+          <t>https://artportalen.se/Sighting/135494402</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135522444</v>
+        <v>135494411</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>79468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,13 +3869,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>852196</v>
+        <v>852712</v>
       </c>
       <c r="R30" t="n">
-        <v>7375416</v>
+        <v>7375445</v>
       </c>
       <c r="S30" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3929,27 +3929,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522444</t>
+          <t>https://artportalen.se/Sighting/135494411</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135522449</v>
+        <v>135494431</v>
       </c>
       <c r="B31" t="n">
-        <v>58143</v>
+        <v>80063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,13 +3981,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>852030</v>
+        <v>852101</v>
       </c>
       <c r="R31" t="n">
-        <v>7375425</v>
+        <v>7375449</v>
       </c>
       <c r="S31" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4041,49 +4041,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522449</t>
+          <t>https://artportalen.se/Sighting/135494431</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135494429</v>
+        <v>135522443</v>
       </c>
       <c r="B32" t="n">
-        <v>98162</v>
+        <v>80063</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4093,13 +4093,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>852147</v>
+        <v>852263</v>
       </c>
       <c r="R32" t="n">
-        <v>7375437</v>
+        <v>7375416</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4153,27 +4153,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494429</t>
+          <t>https://artportalen.se/Sighting/135522443</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135494393</v>
+        <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>79467</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,37 +4181,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>852762</v>
+        <v>852494</v>
       </c>
       <c r="R33" t="n">
-        <v>7375449</v>
+        <v>7375411</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,14 +4255,19 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4265,65 +4275,70 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494393</t>
+          <t>https://artportalen.se/Sighting/136948338</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135494406</v>
+        <v>135494438</v>
       </c>
       <c r="B34" t="n">
-        <v>79467</v>
+        <v>57169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>260591</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>852733</v>
+        <v>852178</v>
       </c>
       <c r="R34" t="n">
-        <v>7375489</v>
+        <v>7375380</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4352,7 +4367,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4377,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,54 +4403,59 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494406</t>
+          <t>https://artportalen.se/Sighting/135494438</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135494409</v>
+        <v>136044719</v>
       </c>
       <c r="B35" t="n">
-        <v>79467</v>
+        <v>57193</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>260591</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>852761</v>
+        <v>852790</v>
       </c>
       <c r="R35" t="n">
-        <v>7375492</v>
+        <v>7375455</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4459,22 +4479,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4489,27 +4499,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494409</t>
+          <t>https://artportalen.se/Sighting/136044719</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135494412</v>
+        <v>135522444</v>
       </c>
       <c r="B36" t="n">
-        <v>79467</v>
+        <v>58143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,21 +4527,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,13 +4551,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>852548</v>
+        <v>852196</v>
       </c>
       <c r="R36" t="n">
-        <v>7375432</v>
+        <v>7375416</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4576,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4596,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4601,27 +4611,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494412</t>
+          <t>https://artportalen.se/Sighting/135522444</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135494413</v>
+        <v>135522449</v>
       </c>
       <c r="B37" t="n">
-        <v>79467</v>
+        <v>58143</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4629,21 +4639,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,13 +4663,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>852548</v>
+        <v>852030</v>
       </c>
       <c r="R37" t="n">
-        <v>7375398</v>
+        <v>7375425</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4708,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4713,49 +4723,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494413</t>
+          <t>https://artportalen.se/Sighting/135522449</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135494427</v>
+        <v>135494429</v>
       </c>
       <c r="B38" t="n">
-        <v>79467</v>
+        <v>98162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>852235</v>
+        <v>852147</v>
       </c>
       <c r="R38" t="n">
-        <v>7375410</v>
+        <v>7375437</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4800,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4836,13 +4846,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494427</t>
+          <t>https://artportalen.se/Sighting/135494429</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135494428</v>
+        <v>135494393</v>
       </c>
       <c r="B39" t="n">
         <v>79467</v>
@@ -4877,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>852154</v>
+        <v>852762</v>
       </c>
       <c r="R39" t="n">
-        <v>7375442</v>
+        <v>7375449</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4912,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4948,13 +4958,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494428</t>
+          <t>https://artportalen.se/Sighting/135494393</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135522446</v>
+        <v>135494406</v>
       </c>
       <c r="B40" t="n">
         <v>79467</v>
@@ -4989,13 +4999,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>852123</v>
+        <v>852733</v>
       </c>
       <c r="R40" t="n">
-        <v>7375442</v>
+        <v>7375489</v>
       </c>
       <c r="S40" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5024,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,7 +5044,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5049,16 +5059,688 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494406</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135494409</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>852761</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7375492</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494409</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135494412</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7375432</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494412</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135494413</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7375398</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494413</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135494427</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>852235</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7375410</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494427</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135494428</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>852154</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494428</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135522446</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>852123</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S46" t="n">
+        <v>68</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135522446</t>
         </is>
@@ -5105,6 +5787,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4199,11 +4199,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -2596,7 +2596,7 @@
         <v>136948350</v>
       </c>
       <c r="B19" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136948353</v>
       </c>
       <c r="B20" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136948360</v>
       </c>
       <c r="B24" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136948358</v>
       </c>
       <c r="B25" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136948359</v>
       </c>
       <c r="B26" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>136948338</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
